--- a/Data/GP2_ADG.xlsx
+++ b/Data/GP2_ADG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Guinea-Pig-data_2\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D27DDE-98B2-414C-AEC2-86DF184C67DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD1FDB0-9497-4B65-80F1-7AF5235C4590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="360" windowWidth="19185" windowHeight="10065" xr2:uid="{5BF3FBCD-7C23-4EBC-BE7D-1A32EADF7981}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{5BF3FBCD-7C23-4EBC-BE7D-1A32EADF7981}"/>
   </bookViews>
   <sheets>
     <sheet name="adg_table_by_diet_sex_week" sheetId="1" r:id="rId1"/>
@@ -955,12 +955,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F0A08BD-57D1-45FC-8A2A-5436517A636E}">
   <dimension ref="A1:G70"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="7" width="8.7109375" style="1"/>
+    <col min="1" max="3" width="8.7265625" style="1"/>
+    <col min="4" max="4" width="11.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -983,7 +985,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1006,7 +1008,7 @@
         <v>3.6070729208998999</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1029,7 +1031,7 @@
         <v>4.0917482361599298</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1052,7 +1054,7 @@
         <v>0.78990225865691199</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1075,7 +1077,7 @@
         <v>1.0045249099870901</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1098,7 +1100,7 @@
         <v>1.59328238326872</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1121,7 +1123,7 @@
         <v>0.85935689551562999</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1144,7 +1146,7 @@
         <v>1.7168215725442599</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1167,7 +1169,7 @@
         <v>0.75713323058955295</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -1190,7 +1192,7 @@
         <v>0.58680678350388904</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -1213,7 +1215,7 @@
         <v>0.80841660977863705</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>4</v>
       </c>
@@ -1236,7 +1238,7 @@
         <v>1.02950795106943</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>4</v>
       </c>
@@ -1259,7 +1261,7 @@
         <v>0.83511374434049002</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
@@ -1282,7 +1284,7 @@
         <v>0.50178818561217098</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
@@ -1305,7 +1307,7 @@
         <v>0.61943211502529905</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>4</v>
       </c>
@@ -1328,7 +1330,7 @@
         <v>0.81411861276245101</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
@@ -1351,7 +1353,7 @@
         <v>0.44926243410046801</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>4</v>
       </c>
@@ -1374,7 +1376,7 @@
         <v>0.31179569158020998</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>4</v>
       </c>
@@ -1397,7 +1399,7 @@
         <v>0.31179569158020998</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
@@ -1420,7 +1422,7 @@
         <v>1.3775327117284999</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>7</v>
       </c>
@@ -1443,7 +1445,7 @@
         <v>0.766356044734813</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -1466,7 +1468,7 @@
         <v>0.64866861728982095</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>7</v>
       </c>
@@ -1489,7 +1491,7 @@
         <v>0.54701830402950002</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
@@ -1512,7 +1514,7 @@
         <v>0.67134413518388902</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
@@ -1535,7 +1537,7 @@
         <v>0.45796057816853902</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>7</v>
       </c>
@@ -1558,7 +1560,7 @@
         <v>0.61465935480473999</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>7</v>
       </c>
@@ -1581,7 +1583,7 @@
         <v>0.61465935480473999</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>7</v>
       </c>
@@ -1604,7 +1606,7 @@
         <v>8.2653250188748402</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>7</v>
       </c>
@@ -1627,7 +1629,7 @@
         <v>7.5407511699430199</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>7</v>
       </c>
@@ -1650,7 +1652,7 @@
         <v>0.97535129758005901</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>7</v>
       </c>
@@ -1673,7 +1675,7 @@
         <v>0.50898451178415205</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>7</v>
       </c>
@@ -1696,7 +1698,7 @@
         <v>1.4822284741156999</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>7</v>
       </c>
@@ -1719,7 +1721,7 @@
         <v>0.924694755853811</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>7</v>
       </c>
@@ -1742,7 +1744,7 @@
         <v>2.0944649160925199</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>7</v>
       </c>
@@ -1765,7 +1767,7 @@
         <v>1.7283196212032701</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>7</v>
       </c>
@@ -1788,7 +1790,7 @@
         <v>3.5101793623556099</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>7</v>
       </c>
@@ -1811,7 +1813,7 @@
         <v>3.5101793623556099</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>8</v>
       </c>
@@ -1834,7 +1836,7 @@
         <v>1.2633514717983401</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>8</v>
       </c>
@@ -1857,7 +1859,7 @@
         <v>1.5049887646284399</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>8</v>
       </c>
@@ -1880,7 +1882,7 @@
         <v>1.4996598253726527</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>8</v>
       </c>
@@ -1903,7 +1905,7 @@
         <v>1.66137936844529</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>8</v>
       </c>
@@ -1926,7 +1928,7 @@
         <v>1.1644239322421699</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>8</v>
       </c>
@@ -1949,7 +1951,7 @@
         <v>0.61177703211728895</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>8</v>
       </c>
@@ -1972,7 +1974,7 @@
         <v>0.61177703211728895</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>8</v>
       </c>
@@ -1995,7 +1997,7 @@
         <v>1.3047010760933599</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>8</v>
       </c>
@@ -2018,7 +2020,7 @@
         <v>1.1057056724163099</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>8</v>
       </c>
@@ -2041,7 +2043,7 @@
         <v>1.4785141295375299</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>8</v>
       </c>
@@ -2064,7 +2066,7 @@
         <v>1.0099966447836199</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>8</v>
       </c>
@@ -2087,7 +2089,7 @@
         <v>0.62984078981036495</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>8</v>
       </c>
@@ -2110,7 +2112,7 @@
         <v>0.55793142764514003</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>8</v>
       </c>
@@ -2133,7 +2135,7 @@
         <v>0.76120172590667801</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>8</v>
       </c>
@@ -2156,7 +2158,7 @@
         <v>0.430221690466491</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>8</v>
       </c>
@@ -2179,7 +2181,7 @@
         <v>0.430221690466491</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>9</v>
       </c>
@@ -2202,7 +2204,7 @@
         <v>0.65222452069576797</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>9</v>
       </c>
@@ -2225,7 +2227,7 @@
         <v>0.53241843295954905</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>9</v>
       </c>
@@ -2248,7 +2250,7 @@
         <v>0.68140178310793598</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>9</v>
       </c>
@@ -2271,7 +2273,7 @@
         <v>0.84795338510478102</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>9</v>
       </c>
@@ -2294,7 +2296,7 @@
         <v>1.0429441146599601</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>9</v>
       </c>
@@ -2317,7 +2319,7 @@
         <v>1.2731751869594901</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>9</v>
       </c>
@@ -2340,7 +2342,7 @@
         <v>0.65364391256362697</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>9</v>
       </c>
@@ -2363,7 +2365,7 @@
         <v>0.65364391256362697</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>9</v>
       </c>
@@ -2386,7 +2388,7 @@
         <v>0.999421601435033</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>9</v>
       </c>
@@ -2409,7 +2411,7 @@
         <v>0.505323138123421</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>9</v>
       </c>
@@ -2432,7 +2434,7 @@
         <v>0.66366671962607005</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>9</v>
       </c>
@@ -2455,7 +2457,7 @@
         <v>0.347325381501151</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>9</v>
       </c>
@@ -2478,7 +2480,7 @@
         <v>0.56706668554089801</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>9</v>
       </c>
@@ -2501,7 +2503,7 @@
         <v>1.4768047876928001</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>9</v>
       </c>
@@ -2524,7 +2526,7 @@
         <v>1.5891925244659899</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>9</v>
       </c>
@@ -2547,7 +2549,7 @@
         <v>0.64382642975830695</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>9</v>
       </c>

--- a/Data/GP2_ADG.xlsx
+++ b/Data/GP2_ADG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Guinea-Pig-data_2\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD1FDB0-9497-4B65-80F1-7AF5235C4590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5155767-D666-4B60-880A-FC149C3523DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{5BF3FBCD-7C23-4EBC-BE7D-1A32EADF7981}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" xr2:uid="{5BF3FBCD-7C23-4EBC-BE7D-1A32EADF7981}"/>
   </bookViews>
   <sheets>
     <sheet name="adg_table_by_diet_sex_week" sheetId="1" r:id="rId1"/>
@@ -955,14 +955,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F0A08BD-57D1-45FC-8A2A-5436517A636E}">
   <dimension ref="A1:G70"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="8.7265625" style="1"/>
-    <col min="4" max="4" width="11.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="8.7265625" style="1"/>
+    <col min="1" max="3" width="8.7109375" style="1"/>
+    <col min="4" max="4" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -985,7 +985,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>3.6070729208998999</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>4.0917482361599298</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1054,7 +1054,7 @@
         <v>0.78990225865691199</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>1.0045249099870901</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>1.59328238326872</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>0.85935689551562999</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>1.7168215725442599</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>0.75713323058955295</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>0.58680678350388904</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>0.80841660977863705</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>4</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>1.02950795106943</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>4</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>0.83511374434049002</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
@@ -1284,7 +1284,7 @@
         <v>0.50178818561217098</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>0.61943211502529905</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>4</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>0.81411861276245101</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
@@ -1353,7 +1353,7 @@
         <v>0.44926243410046801</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>4</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>0.31179569158020998</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>4</v>
       </c>
@@ -1399,7 +1399,7 @@
         <v>0.31179569158020998</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
@@ -1422,7 +1422,7 @@
         <v>1.3775327117284999</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>7</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>0.766356044734813</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>0.64866861728982095</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>7</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>0.54701830402950002</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>0.67134413518388902</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
@@ -1537,7 +1537,7 @@
         <v>0.45796057816853902</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>7</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>0.61465935480473999</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>7</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>0.61465935480473999</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>7</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>8.2653250188748402</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>7</v>
       </c>
@@ -1629,7 +1629,7 @@
         <v>7.5407511699430199</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>7</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>0.97535129758005901</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>7</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>0.50898451178415205</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>7</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>1.4822284741156999</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>7</v>
       </c>
@@ -1721,7 +1721,7 @@
         <v>0.924694755853811</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>7</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>2.0944649160925199</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>7</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>1.7283196212032701</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>7</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>3.5101793623556099</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>7</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>3.5101793623556099</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>8</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>1.2633514717983401</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>8</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>1.5049887646284399</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>8</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>1.4996598253726527</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>8</v>
       </c>
@@ -1905,7 +1905,7 @@
         <v>1.66137936844529</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>8</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>1.1644239322421699</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>8</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>0.61177703211728895</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>8</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>0.61177703211728895</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>8</v>
       </c>
@@ -1997,7 +1997,7 @@
         <v>1.3047010760933599</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>8</v>
       </c>
@@ -2020,7 +2020,7 @@
         <v>1.1057056724163099</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>8</v>
       </c>
@@ -2043,7 +2043,7 @@
         <v>1.4785141295375299</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>8</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>1.0099966447836199</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>8</v>
       </c>
@@ -2089,7 +2089,7 @@
         <v>0.62984078981036495</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>8</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>0.55793142764514003</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>8</v>
       </c>
@@ -2135,7 +2135,7 @@
         <v>0.76120172590667801</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>8</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>0.430221690466491</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>8</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>0.430221690466491</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>9</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>0.65222452069576797</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>9</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>0.53241843295954905</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>9</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>0.68140178310793598</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>9</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>0.84795338510478102</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>9</v>
       </c>
@@ -2296,7 +2296,7 @@
         <v>1.0429441146599601</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>9</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>1.2731751869594901</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>9</v>
       </c>
@@ -2342,7 +2342,7 @@
         <v>0.65364391256362697</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>9</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>0.65364391256362697</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>9</v>
       </c>
@@ -2388,7 +2388,7 @@
         <v>0.999421601435033</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>9</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>0.505323138123421</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>9</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>0.66366671962607005</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>9</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>0.347325381501151</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>9</v>
       </c>
@@ -2480,7 +2480,7 @@
         <v>0.56706668554089801</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>9</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>1.4768047876928001</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>9</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>1.5891925244659899</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>9</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>0.64382642975830695</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>9</v>
       </c>
